--- a/public/templates/examples/A-004-AssetCriticalityRankingMatrix-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-004-AssetCriticalityRankingMatrix-EXAMPLE-S.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -224,12 +224,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -368,7 +368,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -402,7 +402,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-004-AssetCriticalityRankingMatrix-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-004-AssetCriticalityRankingMatrix-EXAMPLE-S.xlsx
@@ -4,19 +4,24 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$19:$19</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Aptos"/>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -142,6 +147,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -612,7 +623,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -804,7 +815,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
@@ -965,7 +976,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -1016,13 +1027,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
+      <c r="K20" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>AST-002</t>
@@ -1073,13 +1082,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
+      <c r="K21" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>AST-003</t>
@@ -1130,13 +1137,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
+      <c r="K22" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="23" ht="34.7" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>AST-004</t>
@@ -1187,13 +1192,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
+      <c r="K23" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>AST-005</t>
@@ -1244,13 +1247,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
+      <c r="K24" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="25" ht="34.7" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>AST-006</t>
@@ -1301,13 +1302,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
+      <c r="K25" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>AST-007</t>
@@ -1358,13 +1357,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
+      <c r="K26" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>AST-008</t>
@@ -1415,13 +1412,11 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
+      <c r="K27" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>AST-009</t>
@@ -1472,10 +1467,8 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="K28" s="14">
+        <v>46034</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
@@ -1529,13 +1522,11 @@
           <t>ESInet Provider</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
+      <c r="K29" s="14">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="30" ht="34.7" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>AST-011</t>
@@ -1586,10 +1577,8 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="K30" s="14">
+        <v>46034</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1"/>
@@ -1608,7 +1597,6 @@
       </c>
       <c r="C33" s="11">
         <f>COUNTA(A20:A30)</f>
-        <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -1619,7 +1607,6 @@
       </c>
       <c r="C34" s="11">
         <f>COUNTIF(F20:F30,"Critical")</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -1630,7 +1617,6 @@
       </c>
       <c r="C35" s="11">
         <f>COUNTIF(F20:F30,"Important")</f>
-        <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -1641,7 +1627,6 @@
       </c>
       <c r="C36" s="11">
         <f>COUNTIF(F20:F30,"Supporting")</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1"/>
@@ -1652,7 +1637,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="34.7" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Tiers set here drive RTO/RPO targets, backup priority, logging scope, and encryption tiering across the program. Assets are drawn from the Master Asset Inventory; the two are kept in step.</t>
@@ -1727,10 +1712,8 @@
           <t>Tracy Holloway</t>
         </is>
       </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D47" s="15">
+        <v>46042</v>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
@@ -1749,10 +1732,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D48" s="15">
+        <v>46042</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1"/>
@@ -1763,7 +1744,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="17" customHeight="1">
+    <row r="51" ht="34.7" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1785,16 +1766,14 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="17" customHeight="1">
+    <row r="52" ht="34.7" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="B52" s="14">
+        <v>46042</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
@@ -1834,7 +1813,8 @@
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="C4:K4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>